--- a/LanguageAnalysis/bin/Debug/xlsxDict.xlsx
+++ b/LanguageAnalysis/bin/Debug/xlsxDict.xlsx
@@ -12,207 +12,231 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>Назва</t>
   </si>
   <si>
-    <t>Кількість слів</t>
-  </si>
-  <si>
-    <t>Кількість унікальних слів</t>
+    <t>Кількість символів</t>
+  </si>
+  <si>
+    <t>Кількість унікальних символів</t>
   </si>
   <si>
     <t>+LOTR_en_old</t>
   </si>
   <si>
-    <t>479264</t>
-  </si>
-  <si>
-    <t>14309</t>
+    <t>2506509</t>
+  </si>
+  <si>
+    <t>66</t>
   </si>
   <si>
     <t>+LOTR_en_old_space&amp;paragraph</t>
   </si>
   <si>
+    <t>2476862</t>
+  </si>
+  <si>
     <t>+monkey_text_M5k_L1kk</t>
   </si>
   <si>
-    <t>154794</t>
-  </si>
-  <si>
-    <t>123632</t>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>4360</t>
   </si>
   <si>
     <t>arabic_shrt</t>
   </si>
   <si>
-    <t>4</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>arabic_هل كرم المصريون القدامى المرأة أ</t>
   </si>
   <si>
-    <t>2557</t>
-  </si>
-  <si>
-    <t>1337</t>
+    <t>16393</t>
+  </si>
+  <si>
+    <t>85</t>
   </si>
   <si>
     <t>belorus_shrt</t>
   </si>
   <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>belorus_Г_сторыя хваробы</t>
   </si>
   <si>
-    <t>21073</t>
-  </si>
-  <si>
-    <t>5804</t>
+    <t>130063</t>
   </si>
   <si>
     <t>bosnian_Vens_Myesechev_mo_ats</t>
   </si>
   <si>
-    <t>10571</t>
-  </si>
-  <si>
-    <t>3840</t>
+    <t>69068</t>
+  </si>
+  <si>
+    <t>69</t>
   </si>
   <si>
     <t>chinese_世說新語</t>
   </si>
   <si>
-    <t>57307</t>
-  </si>
-  <si>
-    <t>5765</t>
+    <t>81383</t>
+  </si>
+  <si>
+    <t>3108</t>
   </si>
   <si>
     <t>czech_Burroughs_E_R-Tarzan-20.pdb</t>
   </si>
   <si>
-    <t>38358</t>
-  </si>
-  <si>
-    <t>8407</t>
+    <t>234062</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>english0!!!</t>
   </si>
   <si>
-    <t>7300</t>
-  </si>
-  <si>
-    <t>1830</t>
+    <t>42407</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>english0_space&amp;paragraph!!!</t>
   </si>
   <si>
+    <t>42744</t>
+  </si>
+  <si>
     <t>farsi_abusaeed_norm</t>
   </si>
   <si>
-    <t>21762</t>
-  </si>
-  <si>
-    <t>4535</t>
+    <t>88789</t>
+  </si>
+  <si>
+    <t>34</t>
   </si>
   <si>
     <t>farsi_shrt</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>76</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>greek_Αι δύο διαθήκαι</t>
   </si>
   <si>
-    <t>25799</t>
-  </si>
-  <si>
-    <t>7058</t>
+    <t>156865</t>
+  </si>
+  <si>
+    <t>73</t>
   </si>
   <si>
     <t>hebrew_Hunger_book1</t>
   </si>
   <si>
-    <t>19323</t>
-  </si>
-  <si>
-    <t>6786</t>
+    <t>105464</t>
+  </si>
+  <si>
+    <t>121</t>
   </si>
   <si>
     <t>hebrew_shrt</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>Hindi_historyप्राचीन_भारत_का_इतिहास_पाषाणकाल_से_1200_ईस्वी_तक_डॉ_मोहनलाल_गुप्ता</t>
   </si>
   <si>
-    <t>558</t>
-  </si>
-  <si>
-    <t>233</t>
+    <t>2915</t>
+  </si>
+  <si>
+    <t>91</t>
   </si>
   <si>
     <t>japaneseお目出たき人 by Saneatsu Mushanokoji</t>
   </si>
   <si>
-    <t>32841</t>
-  </si>
-  <si>
-    <t>2879</t>
+    <t>52164</t>
+  </si>
+  <si>
+    <t>1238</t>
   </si>
   <si>
     <t>korean_episode-2</t>
   </si>
   <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>902</t>
+    <t>5251</t>
+  </si>
+  <si>
+    <t>566</t>
   </si>
   <si>
     <t>napoletano-calabrese_Il pastor fido in lingua napolitana</t>
   </si>
   <si>
-    <t>37832</t>
-  </si>
-  <si>
-    <t>7018</t>
+    <t>210014</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>napoletano_shrt</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>telugu_Subhalekha</t>
   </si>
   <si>
-    <t>17939</t>
-  </si>
-  <si>
-    <t>7038</t>
+    <t>145527</t>
+  </si>
+  <si>
+    <t>106</t>
   </si>
   <si>
     <t>thai_Батько й Мати ростять дiтей</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>204</t>
+    <t>5647</t>
+  </si>
+  <si>
+    <t>82</t>
   </si>
   <si>
     <t>vietnamese_Chúa Jesus Là Ai</t>
   </si>
   <si>
-    <t>43991</t>
-  </si>
-  <si>
-    <t>2436</t>
+    <t>199254</t>
+  </si>
+  <si>
+    <t>123</t>
   </si>
 </sst>
 </file>
@@ -262,8 +286,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="140.376724243164" customWidth="1"/>
-    <col min="2" max="2" width="15.3388967514038" customWidth="1"/>
-    <col min="3" max="3" width="25.651050567627" customWidth="1"/>
+    <col min="2" max="2" width="19.4864139556885" customWidth="1"/>
+    <col min="3" max="3" width="30.1125774383545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -293,7 +317,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>5</v>
@@ -301,255 +325,255 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
